--- a/backend/data/financials_by_company/1530.TW.xlsx
+++ b/backend/data/financials_by_company/1530.TW.xlsx
@@ -662,576 +662,576 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-29505.348868</v>
+        <v>-1904000</v>
       </c>
       <c r="C2" t="n">
-        <v>0.024008</v>
+        <v>0.2</v>
       </c>
       <c r="D2" t="n">
-        <v>599943000</v>
+        <v>381549000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1229000</v>
+        <v>-9520000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1229000</v>
+        <v>-9520000</v>
       </c>
       <c r="G2" t="n">
-        <v>452501000</v>
+        <v>130860000</v>
       </c>
       <c r="H2" t="n">
-        <v>109888000</v>
+        <v>119788000</v>
       </c>
       <c r="I2" t="n">
-        <v>1639155000</v>
+        <v>2951020000</v>
       </c>
       <c r="J2" t="n">
-        <v>598714000</v>
+        <v>372029000</v>
       </c>
       <c r="K2" t="n">
-        <v>488826000</v>
+        <v>252241000</v>
       </c>
       <c r="L2" t="n">
-        <v>-8206000</v>
+        <v>-10215000</v>
       </c>
       <c r="M2" t="n">
-        <v>31346000</v>
+        <v>14441000</v>
       </c>
       <c r="N2" t="n">
-        <v>23140000</v>
+        <v>4226000</v>
       </c>
       <c r="O2" t="n">
-        <v>453700494.651132</v>
+        <v>138476000</v>
       </c>
       <c r="P2" t="n">
-        <v>452501000</v>
+        <v>130860000</v>
       </c>
       <c r="Q2" t="n">
-        <v>2000800000</v>
+        <v>3355237000</v>
       </c>
       <c r="R2" t="n">
-        <v>97100000</v>
+        <v>96955000</v>
       </c>
       <c r="S2" t="n">
         <v>96594000</v>
       </c>
       <c r="T2" t="n">
-        <v>4.66</v>
+        <v>1.35</v>
       </c>
       <c r="U2" t="n">
-        <v>4.68</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>452501000</v>
+        <v>130860000</v>
       </c>
       <c r="W2" t="n">
-        <v>452501000</v>
+        <v>130860000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>452501000</v>
+        <v>130860000</v>
       </c>
       <c r="Z2" t="n">
-        <v>6004000</v>
+        <v>8827000</v>
       </c>
       <c r="AA2" t="n">
-        <v>446497000</v>
+        <v>122033000</v>
       </c>
       <c r="AB2" t="n">
-        <v>446497000</v>
+        <v>122033000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10983000</v>
+        <v>115767000</v>
       </c>
       <c r="AD2" t="n">
-        <v>457480000</v>
+        <v>237800000</v>
       </c>
       <c r="AE2" t="n">
-        <v>543121000</v>
+        <v>-22896000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1229000</v>
+        <v>-9520000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-3076000</v>
+        <v>-1924000</v>
       </c>
       <c r="AH2" t="n">
-        <v>4305000</v>
+        <v>11444000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-8206000</v>
+        <v>-10215000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>31346000</v>
+        <v>14441000</v>
       </c>
       <c r="AK2" t="n">
-        <v>23140000</v>
+        <v>4226000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-83038000</v>
+        <v>275719000</v>
       </c>
       <c r="AM2" t="n">
-        <v>361645000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>404217000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-1924000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>92583000</v>
+        <v>60627000</v>
       </c>
       <c r="AP2" t="n">
-        <v>269062000</v>
+        <v>343590000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>139405000</v>
+        <v>217903000</v>
       </c>
       <c r="AR2" t="n">
-        <v>129657000</v>
+        <v>125687000</v>
       </c>
       <c r="AS2" t="n">
-        <v>278607000</v>
+        <v>679936000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1639155000</v>
+        <v>2951020000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1917762000</v>
+        <v>3630956000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1917762000</v>
+        <v>3630956000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1374470.763381</v>
+        <v>3273539.372493</v>
       </c>
       <c r="C3" t="n">
-        <v>0.190528</v>
+        <v>0.24033</v>
       </c>
       <c r="D3" t="n">
-        <v>375183000</v>
+        <v>590214000</v>
       </c>
       <c r="E3" t="n">
-        <v>7214000</v>
+        <v>13621000</v>
       </c>
       <c r="F3" t="n">
-        <v>7214000</v>
+        <v>13621000</v>
       </c>
       <c r="G3" t="n">
-        <v>210811000</v>
+        <v>354143000</v>
       </c>
       <c r="H3" t="n">
-        <v>114538000</v>
+        <v>118045000</v>
       </c>
       <c r="I3" t="n">
-        <v>2002794000</v>
+        <v>2432617000</v>
       </c>
       <c r="J3" t="n">
-        <v>382397000</v>
+        <v>603835000</v>
       </c>
       <c r="K3" t="n">
-        <v>267859000</v>
+        <v>485790000</v>
       </c>
       <c r="L3" t="n">
-        <v>-2631000</v>
+        <v>-10030000</v>
       </c>
       <c r="M3" t="n">
-        <v>32760000</v>
+        <v>26002000</v>
       </c>
       <c r="N3" t="n">
-        <v>30129000</v>
+        <v>15972000</v>
       </c>
       <c r="O3" t="n">
-        <v>204971470.763381</v>
+        <v>343795539.372493</v>
       </c>
       <c r="P3" t="n">
-        <v>210811000</v>
+        <v>354143000</v>
       </c>
       <c r="Q3" t="n">
-        <v>2335921000</v>
+        <v>2811013000</v>
       </c>
       <c r="R3" t="n">
-        <v>97086000</v>
+        <v>97110000</v>
       </c>
       <c r="S3" t="n">
         <v>96594000</v>
       </c>
       <c r="T3" t="n">
-        <v>2.17</v>
+        <v>3.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.18</v>
+        <v>3.67</v>
       </c>
       <c r="V3" t="n">
-        <v>210811000</v>
+        <v>354143000</v>
       </c>
       <c r="W3" t="n">
-        <v>210811000</v>
+        <v>354143000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>210811000</v>
+        <v>354143000</v>
       </c>
       <c r="Z3" t="n">
-        <v>20505000</v>
+        <v>4856000</v>
       </c>
       <c r="AA3" t="n">
-        <v>190306000</v>
+        <v>349287000</v>
       </c>
       <c r="AB3" t="n">
-        <v>190306000</v>
+        <v>349287000</v>
       </c>
       <c r="AC3" t="n">
-        <v>44793000</v>
+        <v>110501000</v>
       </c>
       <c r="AD3" t="n">
-        <v>235099000</v>
+        <v>459788000</v>
       </c>
       <c r="AE3" t="n">
-        <v>197342000</v>
+        <v>158911000</v>
       </c>
       <c r="AF3" t="n">
-        <v>7214000</v>
+        <v>13621000</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-7214000</v>
+        <v>-13621000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-2631000</v>
+        <v>-10030000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>32760000</v>
+        <v>26002000</v>
       </c>
       <c r="AK3" t="n">
-        <v>30129000</v>
+        <v>15972000</v>
       </c>
       <c r="AL3" t="n">
-        <v>25996000</v>
+        <v>289504000</v>
       </c>
       <c r="AM3" t="n">
-        <v>333127000</v>
+        <v>378396000</v>
       </c>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
-        <v>53729000</v>
+        <v>61671000</v>
       </c>
       <c r="AP3" t="n">
-        <v>279398000</v>
+        <v>316725000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>149424000</v>
+        <v>188205000</v>
       </c>
       <c r="AR3" t="n">
-        <v>129974000</v>
+        <v>128520000</v>
       </c>
       <c r="AS3" t="n">
-        <v>359123000</v>
+        <v>667900000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2002794000</v>
+        <v>2432617000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2361917000</v>
+        <v>3100517000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2361917000</v>
+        <v>3100517000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3273539.372493</v>
+        <v>1374470.763381</v>
       </c>
       <c r="C4" t="n">
-        <v>0.24033</v>
+        <v>0.190528</v>
       </c>
       <c r="D4" t="n">
-        <v>590214000</v>
+        <v>375183000</v>
       </c>
       <c r="E4" t="n">
-        <v>13621000</v>
+        <v>7214000</v>
       </c>
       <c r="F4" t="n">
-        <v>13621000</v>
+        <v>7214000</v>
       </c>
       <c r="G4" t="n">
-        <v>354143000</v>
+        <v>210811000</v>
       </c>
       <c r="H4" t="n">
-        <v>118045000</v>
+        <v>114538000</v>
       </c>
       <c r="I4" t="n">
-        <v>2432617000</v>
+        <v>2002794000</v>
       </c>
       <c r="J4" t="n">
-        <v>603835000</v>
+        <v>382397000</v>
       </c>
       <c r="K4" t="n">
-        <v>485790000</v>
+        <v>267859000</v>
       </c>
       <c r="L4" t="n">
-        <v>-10030000</v>
+        <v>-2631000</v>
       </c>
       <c r="M4" t="n">
-        <v>26002000</v>
+        <v>32760000</v>
       </c>
       <c r="N4" t="n">
-        <v>15972000</v>
+        <v>30129000</v>
       </c>
       <c r="O4" t="n">
-        <v>343795539.372493</v>
+        <v>204971470.763381</v>
       </c>
       <c r="P4" t="n">
-        <v>354143000</v>
+        <v>210811000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2811013000</v>
+        <v>2335921000</v>
       </c>
       <c r="R4" t="n">
-        <v>97110000</v>
+        <v>97086000</v>
       </c>
       <c r="S4" t="n">
         <v>96594000</v>
       </c>
       <c r="T4" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="U4" t="n">
-        <v>3.67</v>
+        <v>2.18</v>
       </c>
       <c r="V4" t="n">
-        <v>354143000</v>
+        <v>210811000</v>
       </c>
       <c r="W4" t="n">
-        <v>354143000</v>
+        <v>210811000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>354143000</v>
+        <v>210811000</v>
       </c>
       <c r="Z4" t="n">
-        <v>4856000</v>
+        <v>20505000</v>
       </c>
       <c r="AA4" t="n">
-        <v>349287000</v>
+        <v>190306000</v>
       </c>
       <c r="AB4" t="n">
-        <v>349287000</v>
+        <v>190306000</v>
       </c>
       <c r="AC4" t="n">
-        <v>110501000</v>
+        <v>44793000</v>
       </c>
       <c r="AD4" t="n">
-        <v>459788000</v>
+        <v>235099000</v>
       </c>
       <c r="AE4" t="n">
-        <v>158911000</v>
+        <v>197342000</v>
       </c>
       <c r="AF4" t="n">
-        <v>13621000</v>
+        <v>7214000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-13621000</v>
+        <v>-7214000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-10030000</v>
+        <v>-2631000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26002000</v>
+        <v>32760000</v>
       </c>
       <c r="AK4" t="n">
-        <v>15972000</v>
+        <v>30129000</v>
       </c>
       <c r="AL4" t="n">
-        <v>289504000</v>
+        <v>25996000</v>
       </c>
       <c r="AM4" t="n">
-        <v>378396000</v>
+        <v>333127000</v>
       </c>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>61671000</v>
+        <v>53729000</v>
       </c>
       <c r="AP4" t="n">
-        <v>316725000</v>
+        <v>279398000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>188205000</v>
+        <v>149424000</v>
       </c>
       <c r="AR4" t="n">
-        <v>128520000</v>
+        <v>129974000</v>
       </c>
       <c r="AS4" t="n">
-        <v>667900000</v>
+        <v>359123000</v>
       </c>
       <c r="AT4" t="n">
-        <v>2432617000</v>
+        <v>2002794000</v>
       </c>
       <c r="AU4" t="n">
-        <v>3100517000</v>
+        <v>2361917000</v>
       </c>
       <c r="AV4" t="n">
-        <v>3100517000</v>
+        <v>2361917000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-1904000</v>
+        <v>-29505.348868</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2</v>
+        <v>0.024008</v>
       </c>
       <c r="D5" t="n">
-        <v>381549000</v>
+        <v>599943000</v>
       </c>
       <c r="E5" t="n">
-        <v>-9520000</v>
+        <v>-1229000</v>
       </c>
       <c r="F5" t="n">
-        <v>-9520000</v>
+        <v>-1229000</v>
       </c>
       <c r="G5" t="n">
-        <v>130860000</v>
+        <v>452501000</v>
       </c>
       <c r="H5" t="n">
-        <v>119788000</v>
+        <v>109888000</v>
       </c>
       <c r="I5" t="n">
-        <v>2951020000</v>
+        <v>1639155000</v>
       </c>
       <c r="J5" t="n">
-        <v>372029000</v>
+        <v>598714000</v>
       </c>
       <c r="K5" t="n">
-        <v>252241000</v>
+        <v>488826000</v>
       </c>
       <c r="L5" t="n">
-        <v>-10215000</v>
+        <v>-8206000</v>
       </c>
       <c r="M5" t="n">
-        <v>14441000</v>
+        <v>31346000</v>
       </c>
       <c r="N5" t="n">
-        <v>4226000</v>
+        <v>23140000</v>
       </c>
       <c r="O5" t="n">
-        <v>138476000</v>
+        <v>453700494.651132</v>
       </c>
       <c r="P5" t="n">
-        <v>130860000</v>
+        <v>452501000</v>
       </c>
       <c r="Q5" t="n">
-        <v>3355237000</v>
+        <v>2000800000</v>
       </c>
       <c r="R5" t="n">
-        <v>96955000</v>
+        <v>97100000</v>
       </c>
       <c r="S5" t="n">
         <v>96594000</v>
       </c>
       <c r="T5" t="n">
-        <v>1.35</v>
+        <v>4.66</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>4.68</v>
       </c>
       <c r="V5" t="n">
-        <v>130860000</v>
+        <v>452501000</v>
       </c>
       <c r="W5" t="n">
-        <v>130860000</v>
+        <v>452501000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>130860000</v>
+        <v>452501000</v>
       </c>
       <c r="Z5" t="n">
-        <v>8827000</v>
+        <v>6004000</v>
       </c>
       <c r="AA5" t="n">
-        <v>122033000</v>
+        <v>446497000</v>
       </c>
       <c r="AB5" t="n">
-        <v>122033000</v>
+        <v>446497000</v>
       </c>
       <c r="AC5" t="n">
-        <v>115767000</v>
+        <v>10983000</v>
       </c>
       <c r="AD5" t="n">
-        <v>237800000</v>
+        <v>457480000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-22896000</v>
+        <v>543121000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-9520000</v>
+        <v>-1229000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1924000</v>
+        <v>-3076000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11444000</v>
+        <v>4305000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-10215000</v>
+        <v>-8206000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14441000</v>
+        <v>31346000</v>
       </c>
       <c r="AK5" t="n">
-        <v>4226000</v>
+        <v>23140000</v>
       </c>
       <c r="AL5" t="n">
-        <v>275719000</v>
+        <v>-83038000</v>
       </c>
       <c r="AM5" t="n">
-        <v>404217000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-1924000</v>
-      </c>
+        <v>361645000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>60627000</v>
+        <v>92583000</v>
       </c>
       <c r="AP5" t="n">
-        <v>343590000</v>
+        <v>269062000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>217903000</v>
+        <v>139405000</v>
       </c>
       <c r="AR5" t="n">
-        <v>125687000</v>
+        <v>129657000</v>
       </c>
       <c r="AS5" t="n">
-        <v>679936000</v>
+        <v>278607000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2951020000</v>
+        <v>1639155000</v>
       </c>
       <c r="AU5" t="n">
-        <v>3630956000</v>
+        <v>1917762000</v>
       </c>
       <c r="AV5" t="n">
-        <v>3630956000</v>
+        <v>1917762000</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>96594171</v>
@@ -1566,46 +1566,46 @@
         <v>96594171</v>
       </c>
       <c r="D2" t="n">
-        <v>1054212000</v>
+        <v>1255976000</v>
       </c>
       <c r="E2" t="n">
-        <v>2029827000</v>
+        <v>2217998000</v>
       </c>
       <c r="F2" t="n">
-        <v>3618561000</v>
+        <v>3025183000</v>
       </c>
       <c r="G2" t="n">
-        <v>5499323000</v>
+        <v>5230854000</v>
       </c>
       <c r="H2" t="n">
-        <v>1582005000</v>
+        <v>1034077000</v>
       </c>
       <c r="I2" t="n">
-        <v>3618561000</v>
+        <v>3025183000</v>
       </c>
       <c r="J2" t="n">
-        <v>165841000</v>
+        <v>24370000</v>
       </c>
       <c r="K2" t="n">
-        <v>3635337000</v>
+        <v>3037226000</v>
       </c>
       <c r="L2" t="n">
-        <v>3635337000</v>
+        <v>3099898000</v>
       </c>
       <c r="M2" t="n">
-        <v>3725353000</v>
+        <v>3156487000</v>
       </c>
       <c r="N2" t="n">
-        <v>90016000</v>
+        <v>119261000</v>
       </c>
       <c r="O2" t="n">
-        <v>3635337000</v>
+        <v>3037226000</v>
       </c>
       <c r="P2" t="n">
-        <v>1895429000</v>
+        <v>1366883000</v>
       </c>
       <c r="Q2" t="n">
-        <v>95516000</v>
+        <v>124495000</v>
       </c>
       <c r="R2" t="n">
         <v>965942000</v>
@@ -1614,136 +1614,138 @@
         <v>965942000</v>
       </c>
       <c r="T2" t="n">
-        <v>2667905000</v>
+        <v>3050793000</v>
       </c>
       <c r="U2" t="n">
-        <v>302606000</v>
+        <v>225560000</v>
       </c>
       <c r="V2" t="n">
-        <v>2275000</v>
+        <v>4173000</v>
       </c>
       <c r="W2" t="n">
-        <v>4549000</v>
+        <v>12794000</v>
       </c>
       <c r="X2" t="n">
-        <v>8772000</v>
+        <v>11698000</v>
       </c>
       <c r="Y2" t="n">
-        <v>128705000</v>
+        <v>121459000</v>
       </c>
       <c r="Z2" t="n">
-        <v>158305000</v>
+        <v>75436000</v>
       </c>
       <c r="AA2" t="n">
-        <v>158305000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>12764000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>62672000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>2365299000</v>
+        <v>2825233000</v>
       </c>
       <c r="AD2" t="n">
-        <v>1105000</v>
+        <v>1242000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1871522000</v>
+        <v>2142562000</v>
       </c>
       <c r="AF2" t="n">
-        <v>7536000</v>
+        <v>11606000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1863986000</v>
+        <v>2130956000</v>
       </c>
       <c r="AH2" t="n">
-        <v>12221000</v>
+        <v>12934000</v>
       </c>
       <c r="AI2" t="n">
-        <v>295771000</v>
+        <v>447532000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>101922000</v>
+        <v>141035000</v>
       </c>
       <c r="AK2" t="n">
-        <v>8227000</v>
+        <v>27390000</v>
       </c>
       <c r="AL2" t="n">
-        <v>185622000</v>
+        <v>279107000</v>
       </c>
       <c r="AM2" t="n">
-        <v>6393258000</v>
+        <v>6207280000</v>
       </c>
       <c r="AN2" t="n">
-        <v>2445954000</v>
+        <v>2347970000</v>
       </c>
       <c r="AO2" t="n">
-        <v>5902000</v>
+        <v>8638000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2764000</v>
+        <v>12931000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>146471000</v>
+        <v>148210000</v>
       </c>
       <c r="AR2" t="n">
-        <v>10576000</v>
+        <v>16829000</v>
       </c>
       <c r="AS2" t="n">
-        <v>10576000</v>
+        <v>16829000</v>
       </c>
       <c r="AT2" t="n">
-        <v>145031000</v>
+        <v>96604000</v>
       </c>
       <c r="AU2" t="n">
-        <v>16776000</v>
+        <v>12043000</v>
       </c>
       <c r="AV2" t="n">
-        <v>2115210000</v>
+        <v>2023042000</v>
       </c>
       <c r="AW2" t="n">
-        <v>2115210000</v>
+        <v>2023042000</v>
       </c>
       <c r="AX2" t="n">
-        <v>3268000</v>
+        <v>3964000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2111942000</v>
+        <v>2019078000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3947304000</v>
+        <v>3859310000</v>
       </c>
       <c r="BA2" t="n">
-        <v>229951000</v>
+        <v>321502000</v>
       </c>
       <c r="BB2" t="n">
-        <v>64561000</v>
+        <v>75973000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1438050000</v>
+        <v>1549646000</v>
       </c>
       <c r="BD2" t="n">
-        <v>123526000</v>
+        <v>261045000</v>
       </c>
       <c r="BE2" t="n">
-        <v>31512000</v>
+        <v>732000</v>
       </c>
       <c r="BF2" t="n">
-        <v>273391000</v>
+        <v>540343000</v>
       </c>
       <c r="BG2" t="n">
-        <v>273391000</v>
+        <v>540343000</v>
       </c>
       <c r="BH2" t="n">
-        <v>1786313000</v>
+        <v>1110069000</v>
       </c>
       <c r="BI2" t="n">
-        <v>976539000</v>
+        <v>172417000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>809774000</v>
+        <v>937652000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>96594171</v>
@@ -1752,43 +1754,43 @@
         <v>96594171</v>
       </c>
       <c r="D3" t="n">
-        <v>1053413000</v>
+        <v>1506782000</v>
       </c>
       <c r="E3" t="n">
-        <v>1920504000</v>
+        <v>2651291000</v>
       </c>
       <c r="F3" t="n">
-        <v>3281196000</v>
+        <v>3242308000</v>
       </c>
       <c r="G3" t="n">
-        <v>5213438000</v>
+        <v>5891629000</v>
       </c>
       <c r="H3" t="n">
-        <v>1364084000</v>
+        <v>1315732000</v>
       </c>
       <c r="I3" t="n">
-        <v>3281196000</v>
+        <v>3242308000</v>
       </c>
       <c r="J3" t="n">
-        <v>918000</v>
+        <v>12338000</v>
       </c>
       <c r="K3" t="n">
-        <v>3293852000</v>
+        <v>3252676000</v>
       </c>
       <c r="L3" t="n">
-        <v>3293852000</v>
+        <v>3252676000</v>
       </c>
       <c r="M3" t="n">
-        <v>3387593000</v>
+        <v>3368195000</v>
       </c>
       <c r="N3" t="n">
-        <v>93741000</v>
+        <v>115519000</v>
       </c>
       <c r="O3" t="n">
-        <v>3293852000</v>
+        <v>3252676000</v>
       </c>
       <c r="P3" t="n">
-        <v>1606748000</v>
+        <v>1595597000</v>
       </c>
       <c r="Q3" t="n">
         <v>95516000</v>
@@ -1800,136 +1802,138 @@
         <v>965942000</v>
       </c>
       <c r="T3" t="n">
-        <v>2574298000</v>
+        <v>3423603000</v>
       </c>
       <c r="U3" t="n">
-        <v>135528000</v>
+        <v>135109000</v>
       </c>
       <c r="V3" t="n">
-        <v>1911000</v>
+        <v>2183000</v>
       </c>
       <c r="W3" t="n">
-        <v>6973000</v>
+        <v>8991000</v>
       </c>
       <c r="X3" t="n">
-        <v>9533000</v>
+        <v>10793000</v>
       </c>
       <c r="Y3" t="n">
-        <v>116831000</v>
+        <v>112224000</v>
       </c>
       <c r="Z3" t="n">
-        <v>280000</v>
+        <v>918000</v>
       </c>
       <c r="AA3" t="n">
-        <v>280000</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
+        <v>918000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>2438770000</v>
+        <v>3288494000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1077000</v>
+        <v>2099000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1920224000</v>
+        <v>2650373000</v>
       </c>
       <c r="AF3" t="n">
-        <v>638000</v>
+        <v>11420000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1919586000</v>
+        <v>2638953000</v>
       </c>
       <c r="AH3" t="n">
-        <v>12935000</v>
+        <v>12445000</v>
       </c>
       <c r="AI3" t="n">
-        <v>331253000</v>
+        <v>397630000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>113517000</v>
+        <v>130896000</v>
       </c>
       <c r="AK3" t="n">
-        <v>52116000</v>
+        <v>64623000</v>
       </c>
       <c r="AL3" t="n">
-        <v>165620000</v>
+        <v>202111000</v>
       </c>
       <c r="AM3" t="n">
-        <v>5961891000</v>
+        <v>6791798000</v>
       </c>
       <c r="AN3" t="n">
-        <v>2159037000</v>
+        <v>2187572000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6605000</v>
+        <v>6544000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3965000</v>
+        <v>7146000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>140108000</v>
+        <v>101283000</v>
       </c>
       <c r="AR3" t="n">
-        <v>12128000</v>
+        <v>10458000</v>
       </c>
       <c r="AS3" t="n">
-        <v>12128000</v>
+        <v>10458000</v>
       </c>
       <c r="AT3" t="n">
-        <v>116713000</v>
+        <v>109850000</v>
       </c>
       <c r="AU3" t="n">
-        <v>12656000</v>
+        <v>10368000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1859449000</v>
+        <v>1929808000</v>
       </c>
       <c r="AW3" t="n">
-        <v>1859449000</v>
+        <v>1929808000</v>
       </c>
       <c r="AX3" t="n">
-        <v>3200000</v>
+        <v>300000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1856249000</v>
+        <v>1929508000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3802854000</v>
+        <v>4604226000</v>
       </c>
       <c r="BA3" t="n">
-        <v>344423000</v>
+        <v>542186000</v>
       </c>
       <c r="BB3" t="n">
-        <v>42490000</v>
+        <v>57859000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1448774000</v>
+        <v>1607007000</v>
       </c>
       <c r="BD3" t="n">
-        <v>169656000</v>
+        <v>396680000</v>
       </c>
       <c r="BE3" t="n">
-        <v>26000</v>
+        <v>143000</v>
       </c>
       <c r="BF3" t="n">
-        <v>394383000</v>
+        <v>491178000</v>
       </c>
       <c r="BG3" t="n">
-        <v>394383000</v>
+        <v>491178000</v>
       </c>
       <c r="BH3" t="n">
-        <v>1403102000</v>
+        <v>1509173000</v>
       </c>
       <c r="BI3" t="n">
-        <v>536929000</v>
+        <v>377002000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>866173000</v>
+        <v>1132171000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>96594171</v>
@@ -1938,43 +1942,43 @@
         <v>96594171</v>
       </c>
       <c r="D4" t="n">
-        <v>1506782000</v>
+        <v>1053413000</v>
       </c>
       <c r="E4" t="n">
-        <v>2651291000</v>
+        <v>1920504000</v>
       </c>
       <c r="F4" t="n">
-        <v>3242308000</v>
+        <v>3281196000</v>
       </c>
       <c r="G4" t="n">
-        <v>5891629000</v>
+        <v>5213438000</v>
       </c>
       <c r="H4" t="n">
-        <v>1315732000</v>
+        <v>1364084000</v>
       </c>
       <c r="I4" t="n">
-        <v>3242308000</v>
+        <v>3281196000</v>
       </c>
       <c r="J4" t="n">
-        <v>12338000</v>
+        <v>918000</v>
       </c>
       <c r="K4" t="n">
-        <v>3252676000</v>
+        <v>3293852000</v>
       </c>
       <c r="L4" t="n">
-        <v>3252676000</v>
+        <v>3293852000</v>
       </c>
       <c r="M4" t="n">
-        <v>3368195000</v>
+        <v>3387593000</v>
       </c>
       <c r="N4" t="n">
-        <v>115519000</v>
+        <v>93741000</v>
       </c>
       <c r="O4" t="n">
-        <v>3252676000</v>
+        <v>3293852000</v>
       </c>
       <c r="P4" t="n">
-        <v>1595597000</v>
+        <v>1606748000</v>
       </c>
       <c r="Q4" t="n">
         <v>95516000</v>
@@ -1986,138 +1990,136 @@
         <v>965942000</v>
       </c>
       <c r="T4" t="n">
-        <v>3423603000</v>
+        <v>2574298000</v>
       </c>
       <c r="U4" t="n">
-        <v>135109000</v>
+        <v>135528000</v>
       </c>
       <c r="V4" t="n">
-        <v>2183000</v>
+        <v>1911000</v>
       </c>
       <c r="W4" t="n">
-        <v>8991000</v>
+        <v>6973000</v>
       </c>
       <c r="X4" t="n">
-        <v>10793000</v>
+        <v>9533000</v>
       </c>
       <c r="Y4" t="n">
-        <v>112224000</v>
+        <v>116831000</v>
       </c>
       <c r="Z4" t="n">
-        <v>918000</v>
+        <v>280000</v>
       </c>
       <c r="AA4" t="n">
-        <v>918000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>280000</v>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>3288494000</v>
+        <v>2438770000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2099000</v>
+        <v>1077000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2650373000</v>
+        <v>1920224000</v>
       </c>
       <c r="AF4" t="n">
-        <v>11420000</v>
+        <v>638000</v>
       </c>
       <c r="AG4" t="n">
-        <v>2638953000</v>
+        <v>1919586000</v>
       </c>
       <c r="AH4" t="n">
-        <v>12445000</v>
+        <v>12935000</v>
       </c>
       <c r="AI4" t="n">
-        <v>397630000</v>
+        <v>331253000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>130896000</v>
+        <v>113517000</v>
       </c>
       <c r="AK4" t="n">
-        <v>64623000</v>
+        <v>52116000</v>
       </c>
       <c r="AL4" t="n">
-        <v>202111000</v>
+        <v>165620000</v>
       </c>
       <c r="AM4" t="n">
-        <v>6791798000</v>
+        <v>5961891000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2187572000</v>
+        <v>2159037000</v>
       </c>
       <c r="AO4" t="n">
-        <v>6544000</v>
+        <v>6605000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7146000</v>
+        <v>3965000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>101283000</v>
+        <v>140108000</v>
       </c>
       <c r="AR4" t="n">
-        <v>10458000</v>
+        <v>12128000</v>
       </c>
       <c r="AS4" t="n">
-        <v>10458000</v>
+        <v>12128000</v>
       </c>
       <c r="AT4" t="n">
-        <v>109850000</v>
+        <v>116713000</v>
       </c>
       <c r="AU4" t="n">
-        <v>10368000</v>
+        <v>12656000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1929808000</v>
+        <v>1859449000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1929808000</v>
+        <v>1859449000</v>
       </c>
       <c r="AX4" t="n">
-        <v>300000</v>
+        <v>3200000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1929508000</v>
+        <v>1856249000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4604226000</v>
+        <v>3802854000</v>
       </c>
       <c r="BA4" t="n">
-        <v>542186000</v>
+        <v>344423000</v>
       </c>
       <c r="BB4" t="n">
-        <v>57859000</v>
+        <v>42490000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1607007000</v>
+        <v>1448774000</v>
       </c>
       <c r="BD4" t="n">
-        <v>396680000</v>
+        <v>169656000</v>
       </c>
       <c r="BE4" t="n">
-        <v>143000</v>
+        <v>26000</v>
       </c>
       <c r="BF4" t="n">
-        <v>491178000</v>
+        <v>394383000</v>
       </c>
       <c r="BG4" t="n">
-        <v>491178000</v>
+        <v>394383000</v>
       </c>
       <c r="BH4" t="n">
-        <v>1509173000</v>
+        <v>1403102000</v>
       </c>
       <c r="BI4" t="n">
-        <v>377002000</v>
+        <v>536929000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1132171000</v>
+        <v>866173000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>96594171</v>
@@ -2126,46 +2128,46 @@
         <v>96594171</v>
       </c>
       <c r="D5" t="n">
-        <v>1255976000</v>
+        <v>1054212000</v>
       </c>
       <c r="E5" t="n">
-        <v>2217998000</v>
+        <v>2029827000</v>
       </c>
       <c r="F5" t="n">
-        <v>3025183000</v>
+        <v>3618561000</v>
       </c>
       <c r="G5" t="n">
-        <v>5230854000</v>
+        <v>5499323000</v>
       </c>
       <c r="H5" t="n">
-        <v>1034077000</v>
+        <v>1582005000</v>
       </c>
       <c r="I5" t="n">
-        <v>3025183000</v>
+        <v>3618561000</v>
       </c>
       <c r="J5" t="n">
-        <v>24370000</v>
+        <v>165841000</v>
       </c>
       <c r="K5" t="n">
-        <v>3037226000</v>
+        <v>3635337000</v>
       </c>
       <c r="L5" t="n">
-        <v>3099898000</v>
+        <v>3635337000</v>
       </c>
       <c r="M5" t="n">
-        <v>3156487000</v>
+        <v>3725353000</v>
       </c>
       <c r="N5" t="n">
-        <v>119261000</v>
+        <v>90016000</v>
       </c>
       <c r="O5" t="n">
-        <v>3037226000</v>
+        <v>3635337000</v>
       </c>
       <c r="P5" t="n">
-        <v>1366883000</v>
+        <v>1895429000</v>
       </c>
       <c r="Q5" t="n">
-        <v>124495000</v>
+        <v>95516000</v>
       </c>
       <c r="R5" t="n">
         <v>965942000</v>
@@ -2174,133 +2176,131 @@
         <v>965942000</v>
       </c>
       <c r="T5" t="n">
-        <v>3050793000</v>
+        <v>2667905000</v>
       </c>
       <c r="U5" t="n">
-        <v>225560000</v>
+        <v>302606000</v>
       </c>
       <c r="V5" t="n">
-        <v>4173000</v>
+        <v>2275000</v>
       </c>
       <c r="W5" t="n">
-        <v>12794000</v>
+        <v>4549000</v>
       </c>
       <c r="X5" t="n">
-        <v>11698000</v>
+        <v>8772000</v>
       </c>
       <c r="Y5" t="n">
-        <v>121459000</v>
+        <v>128705000</v>
       </c>
       <c r="Z5" t="n">
-        <v>75436000</v>
+        <v>158305000</v>
       </c>
       <c r="AA5" t="n">
-        <v>12764000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>62672000</v>
-      </c>
+        <v>158305000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>2825233000</v>
+        <v>2365299000</v>
       </c>
       <c r="AD5" t="n">
-        <v>1242000</v>
+        <v>1105000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2142562000</v>
+        <v>1871522000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11606000</v>
+        <v>7536000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2130956000</v>
+        <v>1863986000</v>
       </c>
       <c r="AH5" t="n">
-        <v>12934000</v>
+        <v>12221000</v>
       </c>
       <c r="AI5" t="n">
-        <v>447532000</v>
+        <v>295771000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>141035000</v>
+        <v>101922000</v>
       </c>
       <c r="AK5" t="n">
-        <v>27390000</v>
+        <v>8227000</v>
       </c>
       <c r="AL5" t="n">
-        <v>279107000</v>
+        <v>185622000</v>
       </c>
       <c r="AM5" t="n">
-        <v>6207280000</v>
+        <v>6393258000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2347970000</v>
+        <v>2445954000</v>
       </c>
       <c r="AO5" t="n">
-        <v>8638000</v>
+        <v>5902000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12931000</v>
+        <v>2764000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>148210000</v>
+        <v>146471000</v>
       </c>
       <c r="AR5" t="n">
-        <v>16829000</v>
+        <v>10576000</v>
       </c>
       <c r="AS5" t="n">
-        <v>16829000</v>
+        <v>10576000</v>
       </c>
       <c r="AT5" t="n">
-        <v>96604000</v>
+        <v>145031000</v>
       </c>
       <c r="AU5" t="n">
-        <v>12043000</v>
+        <v>16776000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2023042000</v>
+        <v>2115210000</v>
       </c>
       <c r="AW5" t="n">
-        <v>2023042000</v>
+        <v>2115210000</v>
       </c>
       <c r="AX5" t="n">
-        <v>3964000</v>
+        <v>3268000</v>
       </c>
       <c r="AY5" t="n">
-        <v>2019078000</v>
+        <v>2111942000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3859310000</v>
+        <v>3947304000</v>
       </c>
       <c r="BA5" t="n">
-        <v>321502000</v>
+        <v>229951000</v>
       </c>
       <c r="BB5" t="n">
-        <v>75973000</v>
+        <v>64561000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1549646000</v>
+        <v>1438050000</v>
       </c>
       <c r="BD5" t="n">
-        <v>261045000</v>
+        <v>123526000</v>
       </c>
       <c r="BE5" t="n">
-        <v>732000</v>
+        <v>31512000</v>
       </c>
       <c r="BF5" t="n">
-        <v>540343000</v>
+        <v>273391000</v>
       </c>
       <c r="BG5" t="n">
-        <v>540343000</v>
+        <v>273391000</v>
       </c>
       <c r="BH5" t="n">
-        <v>1110069000</v>
+        <v>1786313000</v>
       </c>
       <c r="BI5" t="n">
-        <v>172417000</v>
+        <v>976539000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>937652000</v>
+        <v>809774000</v>
       </c>
     </row>
   </sheetData>
@@ -2571,229 +2571,237 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-50610000</v>
+        <v>415938000</v>
       </c>
       <c r="C2" t="n">
+        <v>-229893000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>288718000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-62743000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>937652000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>907808000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>32871000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-3027000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-209780000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1688000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-13894000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-241485000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>58825000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-2580000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-229893000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>227313000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>61405000</v>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
-        <v>37131000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-191074000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>809774000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>866173000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>14778000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-71177000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-147365000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>364000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-32111000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-144891000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37131000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>37131000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>37131000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>61405000</v>
+      </c>
       <c r="U2" t="n">
-        <v>-64276000</v>
+        <v>-271928000</v>
       </c>
       <c r="V2" t="n">
-        <v>1904000</v>
+        <v>-4783000</v>
       </c>
       <c r="W2" t="n">
-        <v>23793000</v>
+        <v>1724000</v>
       </c>
       <c r="X2" t="n">
-        <v>94098000</v>
+        <v>-205540000</v>
       </c>
       <c r="Y2" t="n">
-        <v>122344000</v>
+        <v>8540000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-28246000</v>
+        <v>-214080000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-10350000</v>
+        <v>-7333000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-10350000</v>
+        <v>-7333000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-7380000</v>
+        <v>-4639000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-7380000</v>
+        <v>-4639000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-166341000</v>
+        <v>-51357000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17353000</v>
+        <v>6747000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-183694000</v>
+        <v>-58104000</v>
       </c>
       <c r="AH2" t="n">
-        <v>140464000</v>
+        <v>478681000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-88642000</v>
+        <v>-62093000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24773000</v>
+        <v>4226000</v>
       </c>
       <c r="AK2" t="n">
-        <v>76916000</v>
+        <v>175336000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-92708000</v>
+        <v>234272000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10374000</v>
+        <v>7809000</v>
       </c>
       <c r="AN2" t="n">
-        <v>8926000</v>
+        <v>-19968000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-22071000</v>
+        <v>17707000</v>
       </c>
       <c r="AP2" t="n">
-        <v>10724000</v>
+        <v>-203306000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>165172000</v>
+        <v>151296000</v>
       </c>
       <c r="AR2" t="n">
-        <v>5992000</v>
+        <v>1991000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4305000</v>
+        <v>11444000</v>
       </c>
       <c r="AT2" t="n">
-        <v>109888000</v>
+        <v>119788000</v>
       </c>
       <c r="AU2" t="n">
-        <v>3467000</v>
+        <v>2406000</v>
       </c>
       <c r="AV2" t="n">
-        <v>106421000</v>
+        <v>117382000</v>
       </c>
       <c r="AW2" t="n">
-        <v>-437330000</v>
+        <v>-3648000</v>
       </c>
       <c r="AX2" t="n">
-        <v>-6086000</v>
+        <v>-1451000</v>
       </c>
       <c r="AY2" t="n">
-        <v>457480000</v>
+        <v>237800000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>339818000</v>
+        <v>198301000</v>
       </c>
       <c r="C3" t="n">
-        <v>-587751000</v>
+        <v>-62672000</v>
       </c>
       <c r="D3" t="n">
+        <v>648902000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-23586000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1132171000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>937652000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2219000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>192300000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>402147000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1990000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-25793000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>-144890000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>586230000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>648902000</v>
+      </c>
+      <c r="P3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>-59621000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>866173000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1132171000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-9215000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-256783000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>-785616000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-272000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-31622000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>-154551000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-587751000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-587751000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-587751000</v>
-      </c>
       <c r="Q3" t="n">
+        <v>648902000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-62672000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-62672000</v>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
       <c r="U3" t="n">
-        <v>129394000</v>
+        <v>-431734000</v>
       </c>
       <c r="V3" t="n">
-        <v>3120000</v>
+        <v>7879000</v>
       </c>
       <c r="W3" t="n">
-        <v>23308000</v>
+        <v>18114000</v>
       </c>
       <c r="X3" t="n">
-        <v>160808000</v>
+        <v>-441545000</v>
       </c>
       <c r="Y3" t="n">
-        <v>219959000</v>
+        <v>26327000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-59151000</v>
+        <v>-467872000</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -2802,153 +2810,151 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5079000</v>
+        <v>-1246000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-5079000</v>
+        <v>-1246000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-52763000</v>
+        <v>-14936000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1779000</v>
+        <v>7404000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-54542000</v>
+        <v>-22340000</v>
       </c>
       <c r="AH3" t="n">
-        <v>399439000</v>
+        <v>221887000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-87932000</v>
+        <v>-37909000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>30862000</v>
+        <v>12058000</v>
       </c>
       <c r="AK3" t="n">
-        <v>269402000</v>
+        <v>-312987000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-132638000</v>
+        <v>-140048000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-52259000</v>
+        <v>4729000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-52842000</v>
+        <v>-85954000</v>
       </c>
       <c r="AO3" t="n">
-        <v>15369000</v>
+        <v>18114000</v>
       </c>
       <c r="AP3" t="n">
-        <v>158233000</v>
+        <v>-57361000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>335105000</v>
+        <v>-51447000</v>
       </c>
       <c r="AR3" t="n">
-        <v>1766000</v>
+        <v>24715000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-7214000</v>
+        <v>-13621000</v>
       </c>
       <c r="AT3" t="n">
-        <v>114538000</v>
+        <v>118045000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2752000</v>
+        <v>2965000</v>
       </c>
       <c r="AV3" t="n">
-        <v>111786000</v>
+        <v>115080000</v>
       </c>
       <c r="AW3" t="n">
-        <v>-149843000</v>
+        <v>-20209000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-61000</v>
+        <v>-211000</v>
       </c>
       <c r="AY3" t="n">
-        <v>235099000</v>
+        <v>459788000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>198301000</v>
+        <v>339818000</v>
       </c>
       <c r="C4" t="n">
-        <v>-62672000</v>
+        <v>-587751000</v>
       </c>
       <c r="D4" t="n">
-        <v>648902000</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-23586000</v>
+        <v>-59621000</v>
       </c>
       <c r="F4" t="n">
+        <v>866173000</v>
+      </c>
+      <c r="G4" t="n">
         <v>1132171000</v>
       </c>
-      <c r="G4" t="n">
-        <v>937652000</v>
-      </c>
       <c r="H4" t="n">
-        <v>2219000</v>
+        <v>-9215000</v>
       </c>
       <c r="I4" t="n">
-        <v>192300000</v>
+        <v>-256783000</v>
       </c>
       <c r="J4" t="n">
-        <v>402147000</v>
+        <v>-785616000</v>
       </c>
       <c r="K4" t="n">
-        <v>-1990000</v>
+        <v>-272000</v>
       </c>
       <c r="L4" t="n">
-        <v>-25793000</v>
+        <v>-31622000</v>
       </c>
       <c r="M4" t="n">
-        <v>-144890000</v>
+        <v>-154551000</v>
       </c>
       <c r="N4" t="n">
-        <v>586230000</v>
+        <v>-587751000</v>
       </c>
       <c r="O4" t="n">
-        <v>648902000</v>
+        <v>-587751000</v>
       </c>
       <c r="P4" t="n">
+        <v>-587751000</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>648902000</v>
-      </c>
       <c r="R4" t="n">
-        <v>-62672000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-62672000</v>
-      </c>
-      <c r="T4" t="n">
         <v>0</v>
       </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-431734000</v>
+        <v>129394000</v>
       </c>
       <c r="V4" t="n">
-        <v>7879000</v>
+        <v>3120000</v>
       </c>
       <c r="W4" t="n">
-        <v>18114000</v>
+        <v>23308000</v>
       </c>
       <c r="X4" t="n">
-        <v>-441545000</v>
+        <v>160808000</v>
       </c>
       <c r="Y4" t="n">
-        <v>26327000</v>
+        <v>219959000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-467872000</v>
+        <v>-59151000</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2957,228 +2963,222 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1246000</v>
+        <v>-5079000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1246000</v>
+        <v>-5079000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-14936000</v>
+        <v>-52763000</v>
       </c>
       <c r="AF4" t="n">
-        <v>7404000</v>
+        <v>1779000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-22340000</v>
+        <v>-54542000</v>
       </c>
       <c r="AH4" t="n">
-        <v>221887000</v>
+        <v>399439000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-37909000</v>
+        <v>-87932000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12058000</v>
+        <v>30862000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-312987000</v>
+        <v>269402000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-140048000</v>
+        <v>-132638000</v>
       </c>
       <c r="AM4" t="n">
-        <v>4729000</v>
+        <v>-52259000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-85954000</v>
+        <v>-52842000</v>
       </c>
       <c r="AO4" t="n">
-        <v>18114000</v>
+        <v>15369000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-57361000</v>
+        <v>158233000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-51447000</v>
+        <v>335105000</v>
       </c>
       <c r="AR4" t="n">
-        <v>24715000</v>
+        <v>1766000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-13621000</v>
+        <v>-7214000</v>
       </c>
       <c r="AT4" t="n">
-        <v>118045000</v>
+        <v>114538000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2965000</v>
+        <v>2752000</v>
       </c>
       <c r="AV4" t="n">
-        <v>115080000</v>
+        <v>111786000</v>
       </c>
       <c r="AW4" t="n">
-        <v>-20209000</v>
+        <v>-149843000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-211000</v>
+        <v>-61000</v>
       </c>
       <c r="AY4" t="n">
-        <v>459788000</v>
+        <v>235099000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>415938000</v>
+        <v>-50610000</v>
       </c>
       <c r="C5" t="n">
-        <v>-229893000</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>288718000</v>
+        <v>37131000</v>
       </c>
       <c r="E5" t="n">
-        <v>-62743000</v>
+        <v>-191074000</v>
       </c>
       <c r="F5" t="n">
-        <v>937652000</v>
+        <v>809774000</v>
       </c>
       <c r="G5" t="n">
-        <v>907808000</v>
+        <v>866173000</v>
       </c>
       <c r="H5" t="n">
-        <v>32871000</v>
+        <v>14778000</v>
       </c>
       <c r="I5" t="n">
-        <v>-3027000</v>
+        <v>-71177000</v>
       </c>
       <c r="J5" t="n">
-        <v>-209780000</v>
+        <v>-147365000</v>
       </c>
       <c r="K5" t="n">
-        <v>1688000</v>
+        <v>364000</v>
       </c>
       <c r="L5" t="n">
-        <v>-13894000</v>
+        <v>-32111000</v>
       </c>
       <c r="M5" t="n">
-        <v>-241485000</v>
+        <v>-144891000</v>
       </c>
       <c r="N5" t="n">
-        <v>58825000</v>
+        <v>37131000</v>
       </c>
       <c r="O5" t="n">
-        <v>-2580000</v>
+        <v>37131000</v>
       </c>
       <c r="P5" t="n">
-        <v>-229893000</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>227313000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>61405000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>61405000</v>
-      </c>
+        <v>37131000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-271928000</v>
+        <v>-64276000</v>
       </c>
       <c r="V5" t="n">
-        <v>-4783000</v>
+        <v>1904000</v>
       </c>
       <c r="W5" t="n">
-        <v>1724000</v>
+        <v>23793000</v>
       </c>
       <c r="X5" t="n">
-        <v>-205540000</v>
+        <v>94098000</v>
       </c>
       <c r="Y5" t="n">
-        <v>8540000</v>
+        <v>122344000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-214080000</v>
+        <v>-28246000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-7333000</v>
+        <v>-10350000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-7333000</v>
+        <v>-10350000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4639000</v>
+        <v>-7380000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-4639000</v>
+        <v>-7380000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-51357000</v>
+        <v>-166341000</v>
       </c>
       <c r="AF5" t="n">
-        <v>6747000</v>
+        <v>17353000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-58104000</v>
+        <v>-183694000</v>
       </c>
       <c r="AH5" t="n">
-        <v>478681000</v>
+        <v>140464000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-62093000</v>
+        <v>-88642000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4226000</v>
+        <v>24773000</v>
       </c>
       <c r="AK5" t="n">
-        <v>175336000</v>
+        <v>76916000</v>
       </c>
       <c r="AL5" t="n">
-        <v>234272000</v>
+        <v>-92708000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7809000</v>
+        <v>10374000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-19968000</v>
+        <v>8926000</v>
       </c>
       <c r="AO5" t="n">
-        <v>17707000</v>
+        <v>-22071000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-203306000</v>
+        <v>10724000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>151296000</v>
+        <v>165172000</v>
       </c>
       <c r="AR5" t="n">
-        <v>1991000</v>
+        <v>5992000</v>
       </c>
       <c r="AS5" t="n">
-        <v>11444000</v>
+        <v>4305000</v>
       </c>
       <c r="AT5" t="n">
-        <v>119788000</v>
+        <v>109888000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2406000</v>
+        <v>3467000</v>
       </c>
       <c r="AV5" t="n">
-        <v>117382000</v>
+        <v>106421000</v>
       </c>
       <c r="AW5" t="n">
-        <v>-3648000</v>
+        <v>-437330000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-1451000</v>
+        <v>-6086000</v>
       </c>
       <c r="AY5" t="n">
-        <v>237800000</v>
+        <v>457480000</v>
       </c>
     </row>
   </sheetData>
@@ -3738,182 +3738,182 @@
       </c>
       <c r="DE1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
         <is>
           <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
       <c r="EO1" t="inlineStr">
@@ -4025,34 +4025,34 @@
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>32.5</v>
+        <v>30.55</v>
       </c>
       <c r="U2" t="n">
-        <v>32.5</v>
+        <v>30.55</v>
       </c>
       <c r="V2" t="n">
-        <v>32.5</v>
+        <v>29.5</v>
       </c>
       <c r="W2" t="n">
-        <v>33</v>
+        <v>30.55</v>
       </c>
       <c r="X2" t="n">
-        <v>32.5</v>
+        <v>30.55</v>
       </c>
       <c r="Y2" t="n">
-        <v>32.5</v>
+        <v>30.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>32.5</v>
+        <v>29.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>33</v>
+        <v>30.55</v>
       </c>
       <c r="AB2" t="n">
         <v>1.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.71</v>
+        <v>5.13</v>
       </c>
       <c r="AD2" t="n">
         <v>1751414400</v>
@@ -4064,31 +4064,31 @@
         <v>5.46</v>
       </c>
       <c r="AG2" t="n">
-        <v>54.666664</v>
+        <v>49.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>19.52381</v>
+        <v>17.767859</v>
       </c>
       <c r="AI2" t="n">
-        <v>21000</v>
+        <v>261091</v>
       </c>
       <c r="AJ2" t="n">
-        <v>21000</v>
+        <v>261091</v>
       </c>
       <c r="AK2" t="n">
-        <v>147432</v>
+        <v>182248</v>
       </c>
       <c r="AL2" t="n">
-        <v>734497</v>
+        <v>147041</v>
       </c>
       <c r="AM2" t="n">
-        <v>734497</v>
+        <v>147041</v>
       </c>
       <c r="AN2" t="n">
-        <v>32.65</v>
+        <v>29.8</v>
       </c>
       <c r="AO2" t="n">
-        <v>32.7</v>
+        <v>0</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>3102688512</v>
+        <v>2823635968</v>
       </c>
       <c r="AS2" t="n">
-        <v>3225661231</v>
+        <v>2889851924</v>
       </c>
       <c r="AT2" t="n">
         <v>25.6</v>
@@ -4115,19 +4115,19 @@
         <v>2.392092</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.7057834</v>
+        <v>1.552367</v>
       </c>
       <c r="AY2" t="n">
-        <v>27.538</v>
+        <v>28.857</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27.67075</v>
+        <v>27.88275</v>
       </c>
       <c r="BA2" t="n">
         <v>0.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.003076923</v>
+        <v>0.0032733225</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4138,7 +4138,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>3608700160</v>
+        <v>3353048832</v>
       </c>
       <c r="BF2" t="n">
         <v>0.06002</v>
@@ -4162,7 +4162,7 @@
         <v>33.534</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.97811174</v>
+        <v>0.89014137</v>
       </c>
       <c r="BN2" t="n">
         <v>1767139200</v>
@@ -4191,16 +4191,16 @@
         <v>1471996800</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.984</v>
+        <v>1.843</v>
       </c>
       <c r="BW2" t="n">
-        <v>147.728</v>
+        <v>137.263</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.07570982</v>
+        <v>0.05344832</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BZ2" t="n">
         <v>1.531714</v>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="CC2" t="n">
-        <v>32.8</v>
+        <v>29.85</v>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
@@ -4316,140 +4316,140 @@
       <c r="DE2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
+      <c r="DF2" t="n">
+        <v>946947600000</v>
       </c>
       <c r="DG2" t="n">
-        <v>1780448453</v>
+        <v>-0.69999886</v>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
+          <t>29.5 - 30.55</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>182248</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.16601562</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>25.6 - 36.8</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-6.949999</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.18885867</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>5.344832</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1754305140</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1754654400</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>1</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>AWEA MECHANTRONIC CO</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1782106225</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
           <t>TAI</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DZ2" t="inlineStr">
         <is>
           <t>finmb_9681479</t>
         </is>
       </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Asia/Taipei</t>
         </is>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>CST</t>
         </is>
       </c>
-      <c r="DL2" t="n">
+      <c r="EC2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DM2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>tw_market</t>
         </is>
       </c>
-      <c r="DN2" t="b">
+      <c r="EE2" t="b">
         <v>0</v>
       </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>AWEA MECHANTRONIC CO</t>
-        </is>
-      </c>
-      <c r="DP2" t="inlineStr">
-        <is>
-          <t>Awea mechantronic co.,ltd</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.29999924</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>32.5 - 33.0</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
-      <c r="DU2" t="n">
-        <v>147432</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>7.199999</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.28124994</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>25.6 - 36.8</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>-4</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.108695656</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>7.570982</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1754305140</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1754654400</v>
-      </c>
-      <c r="ED2" t="b">
-        <v>1</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="EF2" t="n">
-        <v>1.68</v>
+        <v>0.99300003</v>
       </c>
       <c r="EG2" t="n">
-        <v>5.261999</v>
+        <v>0.03441106</v>
       </c>
       <c r="EH2" t="n">
-        <v>0.19108139</v>
+        <v>1.9672508</v>
       </c>
       <c r="EI2" t="n">
-        <v>5.1292496</v>
+        <v>0.070554405</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.18536721</v>
+        <v>20</v>
       </c>
       <c r="EK2" t="n">
         <v>20</v>
       </c>
-      <c r="EL2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EM2" t="b">
+      <c r="EL2" t="b">
         <v>0</v>
       </c>
-      <c r="EN2" t="n">
-        <v>946947600000</v>
+      <c r="EM2" t="inlineStr">
+        <is>
+          <t>Awea mechantronic co.,ltd</t>
+        </is>
+      </c>
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EO2" t="n">
-        <v>0.91742885</v>
+        <v>-2.291322</v>
       </c>
       <c r="EP2" t="n">
-        <v>32.8</v>
+        <v>29.85</v>
       </c>
       <c r="EQ2" t="inlineStr"/>
     </row>
